--- a/Employee_Reports_wi52/Herwin Fatalla Mimay Q0496.xlsx
+++ b/Employee_Reports_wi52/Herwin Fatalla Mimay Q0496.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1841,11 +1841,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1878,11 +1878,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1927,11 +1927,11 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -1976,11 +1976,11 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2013,11 +2013,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2050,11 +2050,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2136,11 +2136,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2173,11 +2173,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2210,11 +2210,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7926</v>
+        <v>7918</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7926</v>
+        <v>7918</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7958</v>
+        <v>7950</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7973</v>
+        <v>7965</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7958</v>
+        <v>7950</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7919</v>
+        <v>7911</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7917</v>
+        <v>7909</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7919</v>
+        <v>7911</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7931</v>
+        <v>7923</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7931</v>
+        <v>7923</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7912</v>
+        <v>7904</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7973</v>
+        <v>7965</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7917</v>
+        <v>7909</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7993</v>
+        <v>7985</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7940</v>
+        <v>7932</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7940</v>
+        <v>7932</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>7993</v>
+        <v>7985</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>7912</v>
+        <v>7904</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>7993</v>
+        <v>7985</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
